--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T17:34:51+00:00</t>
+    <t>2026-02-23T07:43:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-update-system-nss/ig/StructureDefinition-fr-core-organization-uf.xlsx
+++ b/nr-update-system-nss/ig/StructureDefinition-fr-core-organization-uf.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot-2</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:28:50+00:00</t>
+    <t>2026-03-25T14:42:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -630,7 +630,7 @@
     <t>shortName</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-short-name|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-short-name|2.2.0}
 </t>
   </si>
   <si>
@@ -701,14 +701,14 @@
     <t>member</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-member|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-member|2.2.0}
 </t>
   </si>
   <si>
-    <t>FR Core Organization Extension - Membre d'organisation</t>
-  </si>
-  <si>
-    <t>Extension permettant de définir des membres d'une organisation.</t>
+    <t>FR Core Organization Extension - quelles sont les entités qui font partie de l'organisation</t>
+  </si>
+  <si>
+    <t>Extension permettant de définir des membres d'une organisation. Les membres sont des organisations filles de la ressources. C'est la relation inverse de partOf.</t>
   </si>
   <si>
     <t>Organization.extension:discplineEquipement</t>
@@ -717,7 +717,7 @@
     <t>discplineEquipement</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-discipline-equipement|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-discipline-equipement|2.2.0}
 </t>
   </si>
   <si>
@@ -733,7 +733,7 @@
     <t>typeActivite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-type-activite|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-type-activite|2.2.0}
 </t>
   </si>
   <si>
@@ -749,7 +749,7 @@
     <t>champActivite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-champ-activite|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-champ-activite|2.2.0}
 </t>
   </si>
   <si>
@@ -765,7 +765,7 @@
     <t>placeHebergement</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-place-hebergement-theorique|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-place-hebergement-theorique|2.2.0}
 </t>
   </si>
   <si>
@@ -781,7 +781,7 @@
     <t>externe</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-uf-externe|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-uf-externe|2.2.0}
 </t>
   </si>
   <si>
@@ -797,7 +797,7 @@
     <t>indicateur</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-uf-indicateur|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-uf-indicateur|2.2.0}
 </t>
   </si>
   <si>
@@ -813,7 +813,7 @@
     <t>demandeuseActe</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-demandeuse-acte|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-demandeuse-acte|2.2.0}
 </t>
   </si>
   <si>
@@ -829,7 +829,7 @@
     <t>executanteActe</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-executante-acte|2.2.0-ballot-2}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-executante-acte|2.2.0}
 </t>
   </si>
   <si>
@@ -951,7 +951,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-type|2.2.0-ballot-2</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-organization-type|2.2.0</t>
   </si>
   <si>
     <t>No equivalent in v2</t>
@@ -1006,7 +1006,7 @@
     <t>Organization.telecom</t>
   </si>
   <si>
-    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0-ballot-2}
+    <t xml:space="preserve">ContactPoint {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-contact-point|2.2.0}
 </t>
   </si>
   <si>
@@ -1042,7 +1042,7 @@
     <t>Organization.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.2.0-ballot-2}
+    <t xml:space="preserve">Address {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-address|2.2.0}
 </t>
   </si>
   <si>
@@ -1078,7 +1078,7 @@
     <t>Organization.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0-ballot-2|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-etablissement|2.2.0-ballot-2)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization-etablissement|2.2.0)
 </t>
   </si>
   <si>
@@ -1631,7 +1631,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="145.421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="132.328125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1646,7 +1646,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="60.875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.33203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -4306,7 +4306,7 @@
         <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>78</v>
